--- a/data/instance_medio_P8_M12_T6.xlsx
+++ b/data/instance_medio_P8_M12_T6.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Produtividade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Demanda" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Estoque" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Custos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Disponibilidade de maquinas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Demanda_Cor" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Estoque_Cor" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="De_Para_Cores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +23,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +52,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,72 +428,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -607,7 +602,7 @@
         <v>30.23557811221317</v>
       </c>
       <c r="N5" t="n">
-        <v>75.50720710260784</v>
+        <v>75.50720710260782</v>
       </c>
     </row>
     <row r="6">
@@ -661,7 +656,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>36.01853978551362</v>
+        <v>36.01853978551361</v>
       </c>
       <c r="E7" t="n">
         <v>39.89413984055313</v>
@@ -749,7 +744,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>79.54253384335023</v>
+        <v>79.54253384335021</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
@@ -771,7 +766,7 @@
         <v>73.44754945271148</v>
       </c>
       <c r="D10" t="n">
-        <v>73.6067983818718</v>
+        <v>73.60679838187178</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
@@ -782,7 +777,7 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>42.41946373242261</v>
+        <v>42.4194637324226</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
@@ -792,7 +787,7 @@
         <v>35.74763095537188</v>
       </c>
       <c r="M10" t="n">
-        <v>76.20878903202676</v>
+        <v>76.20878903202674</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
@@ -811,42 +806,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>01/2024</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>02/2024</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>03/2024</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>04/2024</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>05/2024</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>06/2024</t>
         </is>
@@ -996,7 +991,7 @@
         <v>57681.43820845568</v>
       </c>
       <c r="G7" t="n">
-        <v>64237.61878834399</v>
+        <v>64237.61878834401</v>
       </c>
       <c r="H7" t="n">
         <v>45420.7890730925</v>
@@ -1047,7 +1042,7 @@
         <v>43563.08318885494</v>
       </c>
       <c r="D9" t="n">
-        <v>70467.44460293159</v>
+        <v>70467.44460293157</v>
       </c>
       <c r="E9" t="n">
         <v>69705.59764698839</v>
@@ -1107,17 +1102,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>12/2023</t>
         </is>
@@ -1225,7 +1220,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>51307.58483123815</v>
+        <v>51307.58483123814</v>
       </c>
     </row>
     <row r="10">
@@ -1258,17 +1253,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>CUSTO_UNITARIO</t>
         </is>
@@ -1409,67 +1404,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1732,6 +1727,3884 @@
       <c r="M7" t="n">
         <v>1</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>QUANTIDADE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>PRAZO_ENTREGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5591.081472456401</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>40843.87305745282</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8982.465769936623</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>45305</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6358.756796674752</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>46451.8817488264</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>45328</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10215.79019137218</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4929.675309108932</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45359</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>36012.18002842737</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>45361</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7919.87023246119</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45376</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4851.386170023244</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>45411</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>35440.26354422914</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>45403</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7794.093222153014</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>45410</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6607.810257519983</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>45439</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48271.26284520179</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>45427</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10615.91209944083</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>45436</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3681.67466326188</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>45453</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>26895.30698593861</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>45457</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5914.869386488031</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>45460</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>15246.84405711372</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>45321</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2102.343775004234</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>45318</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3013.529620142165</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>45307</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13843.58286466472</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>45312</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>23579.01398985143</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>45328</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>3251.24288650237</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>45346</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>4660.378030101985</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>45339</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>21408.89175575323</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20807.46494283948</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>45375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2869.081905234519</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>45371</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>4112.583016552907</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>45354</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>18892.42547905572</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>45360</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>23188.50912413505</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>45388</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3197.397286031061</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4583.194976662353</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>45384</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>21054.32746380212</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>45389</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>21851.87047315256</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>45431</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3013.092000504643</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>45434</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4319.009145740623</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>45428</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>19840.70792026409</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>45439</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>22301.51638151584</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>45471</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3075.092390412391</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>45447</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>4407.881390931343</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>20248.97013957106</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>45462</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>50566.07715969493</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>45311</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2822.881342060592</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>45195.17637460699</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>45341</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2523.047610280264</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>45344</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>54183.68695590842</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>45370</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3024.836561254983</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>45354</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>29099.0338278741</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>45398</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1624.470876102887</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>45411</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>47533.94782734816</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>45435</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2653.610918097018</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>45417</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>36904.5884743097</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2060.220608206297</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>45472</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2247.029313544958</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>45297</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>29258.89407006537</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2755.656274383778</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>35881.79937826733</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>45340</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3373.092215517749</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>45365</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>43921.52217484691</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>45376</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>4394.521694237636</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>45412</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>57221.70332413448</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>45406</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2655.753097875177</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>45441</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>34580.94565058866</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>45442</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3363.222629932863</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>45446</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>43793.00887179256</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>45451</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>19157.01302429636</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>18470.16968852076</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>45310</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>22298.51282541515</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>21499.03615791909</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>45325</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>30978.14146986241</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>29867.4709286719</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>45371</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>29367.17509395485</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>45388</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>28314.26311450084</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>45388</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>32705.1033602605</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>45417</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>31532.51542808352</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>45430</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>23124.94811232986</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>22295.84096076265</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>45461</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>14812.79506400831</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>9404.520409100374</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1650.836828862203</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>45313</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>9994.47614838476</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>45308</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>18492.20245666943</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>45344</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>11740.54556628046</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>45345</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2060.894566510347</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>45349</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12477.04269083926</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>45346</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>21948.83708139937</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>45368</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>13935.13414558665</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>45367</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2446.125018816378</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>45359</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>14809.30018588057</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>45370</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>22269.54515653678</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>45387</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>14138.74903561652</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>45410</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2481.866868984598</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>45408</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>15025.68805823717</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>45386</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>16393.54904701699</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>45437</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10408.1279680204</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>45416</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1827.006611894036</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>45435</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11061.04109520104</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>45415</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>19709.29334714232</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>45458</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12513.26645182041</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>45463</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2196.535305302938</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>45465</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>13298.23719347596</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>45456</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>29715.02276519891</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>45320</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>13848.06042365602</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>48066.8852455607</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>45329</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>22400.55935737087</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>47547.21817926727</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>45374</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>22158.37946772112</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>45362</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>29460.49800693451</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>13729.44452153766</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>45409</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>32583.52110153396</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>45438</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>15184.86364943873</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>45436</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>22612.82534708104</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>45463</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10538.23092212807</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>45452</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>8391.133317372656</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>45316</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2231.623907894284</v>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>5749.450244925772</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>45308</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>20367.27386566547</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11380.38324681122</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>45332</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3026.615639868709</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>45327</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>7797.629327407107</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>45350</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>27622.89353741434</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>45327</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>14367.04896039044</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>45354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>3820.920099018745</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>45381</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>9844.037752702639</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>34872.24070339498</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>45365</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10159.74301841228</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2701.986079879127</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>45394</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>6961.269089201293</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>45386</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>24660.10974135925</v>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>45404</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10060.99961173376</v>
+      </c>
+      <c r="E132" s="1" t="n">
+        <v>45418</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2675.725247312625</v>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>45430</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>6893.611922732821</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>45442</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>24420.43603696387</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>45442</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>6107.478661794634</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>45454</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1624.28540735933</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>45467</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>4184.732068936883</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>45462</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>14824.30153694995</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>45458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MODELO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>COR</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ESTOQUE_INICIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5336.730778174198</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>38985.79470167936</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8573.833483641978</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>21162.53649476801</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2918.041707281536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4182.762696688563</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>19214.81760385182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>43913.75176995705</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2451.511319333674</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3131.54587091536</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>40776.31224494922</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>26271.81564768652</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>25329.88271307646</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18937.70369212887</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12023.3905960708</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2110.54420006175</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12777.63089533646</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>34997.66177426273</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16309.92305697541</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10077.7978027525</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2680.192730222137</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6905.121734317751</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LISO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>24461.20923695797</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AZUL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>1.979947317386483</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.926791990005762</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>1.455610825986811</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VERMELHO</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.529144547658173</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>1.738099266794482</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.187822122697827</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9528910871637374</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VERDE</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.671941053147274</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>1.818800036461618</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.755344869491407</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BRANCO</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.498527104159805</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6356610904761991</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5434992548067041</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AMARELO</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.7973063408193468</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.484403558991235</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRETO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.702222716289123</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>0.5858479102298906</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.89169314525842</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.547181175967956</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
